--- a/extracted_urls/motortrend/motortrend_urls.xlsx
+++ b/extracted_urls/motortrend/motortrend_urls.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>This is a ranking/listing page with no substantive engineering narrative, just editorial test-summary marketing and item links.</t>
+          <t>This is a minivan ranking/list page with promotional testing claims, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Body is a rankings/listing page with brief teaser links, not substantive engineering or R&amp;D analysis.</t>
+          <t>This is a ranking/list page with brief teaser links, not substantive engineering analysis or technical article content.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>This is a ranking/listing page with teaser links and no substantive engineering narrative in the body.</t>
+          <t>This is a ranking/listing page with teaser links, not a substantive engineering article, and the body lacks technical R&amp;D detail.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A ranking/listing page with mostly navigation and teaser links, not substantive engineering narrative.</t>
+          <t>This is a ranking/list page with only brief teaser links and no substantive engineering or R&amp;D analysis in the body.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The body gives concrete engineering details on charging architecture, port redesign, voltage conversion, battery chemistry, and validation-based software tuning.</t>
+          <t>Body gives concrete engineering details on charging architecture, port redesign, power conversion, and battery/software tradeoffs for EV development.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Body is mainly a consumer app review for EV road-trip charging, with little engineering or R&amp;D substance.</t>
+          <t>Body is mainly a consumer app review about EV road-trip charging convenience, with little engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Body is a consumer home-charger review focused on installation cost savings, with only light technical detail about load monitoring and breaker protection.</t>
+          <t>Technical, but it’s mainly a home charging product review with limited engineering depth and no substantial automotive R&amp;D or vehicle system development content.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mostly a consumer review of an SUV refresh, with brief mentions of transmission, ADAS, and infotainment but little substantive engineering detail.</t>
+          <t>Mostly a consumer review of a refreshed SUV, with only brief mention of the new transmission and driver-assist tech and little engineering depth.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mostly a facelift and trim/pricing update with no substantive engineering or R&amp;D detail in the body.</t>
+          <t>Mostly a facelift and pricing update with no substantive engineering or R&amp;D detail in the body.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mostly a consumer yearlong road test with performance impressions and option pricing, not engineering-focused R&amp;D or validation content.</t>
+          <t>Mostly a long-term ownership/review piece with performance impressions and option talk, not substantive engineering or R&amp;D analysis in the body.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Body is a styling-and-features first look with no engineering, validation, or technical development detail.</t>
+          <t>This is a styling-and-features first look with no substantive engineering, validation, or architecture detail in the body.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mostly a retirement/profile piece with career highlights and little substantive engineering detail or R&amp;D content.</t>
+          <t>This is a retirement/profile piece with career highlights, not a substantive engineering article with technical development, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Body is mostly a patriotic trim/package announcement with styling and pricing, not engineering or R&amp;D substance.</t>
+          <t>Mostly a patriotic trim/package announcement with colors, badges, and interior cosmetics; no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Body is just a cosmetic special-edition announcement with paint, trim, and badging; no engineering or R&amp;D substance.</t>
+          <t>Body is just a cosmetic anniversary trim and paint announcement, with no engineering, validation, or systems detail.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Body is mainly a profile/interview about design and CMF career history, with little engineering or validation substance beyond color/materials strategy.</t>
+          <t>Mostly a profile/interview about CMF design career and a personal lowrider build, with little engineering or R&amp;D substance beyond general color/materials work.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Body is mainly a vehicle refresh and infotainment feature overview; it mentions MB.OS and sensors, but gives little engineering depth beyond marketing-level system descriptions.</t>
+          <t>Body is mostly a feature refresh and infotainment preview; the MB.OS and sensor stack mention is useful, but there’s little engineering depth or validation detail.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mostly a launch-style overview with styling and interior feature comparisons, offering little engineering, validation, or architecture depth.</t>
+          <t>Mostly a first-look product announcement with styling and feature comparisons; the body has little engineering depth beyond basic EV/driver-assist mentions.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mostly a consumer road test with basic braking/handling results and little engineering depth or development relevance.</t>
+          <t>Mostly a consumer road test with performance numbers and comfort impressions, not substantive engineering or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Body is just a brief auto-show roundup intro with no engineering or R&amp;D substance.</t>
+          <t>Body is just a brief show roundup/listing with no engineering detail or substantive article narrative.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Contains some useful software/architecture details (MB.OS, OTA, driver-monitoring display control), but most of the body is a feature-rich facelift with little engineering depth.</t>
+          <t>Contains some engineering-relevant software and interface changes, but the body is mostly a vehicle refresh with consumer tech and styling, not substantive R&amp;D detail.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mostly a trim-and-spec reveal; the body gives little engineering depth beyond hybrid packaging, suspension retuning, and clearance changes.</t>
+          <t>Mostly a product launch and specs recap; the body adds little engineering depth beyond basic powertrain, clearance, and mpg figures.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The body gives concrete engineering details on MQB evolution, revised electrical architecture, and Gen 5 EA888 turbo/cooling/cam-timing changes with performance and efficiency implications.</t>
+          <t>Body includes meaningful engineering detail on MQB evolution, electrical architecture, and Gen 5 turbo/Miller-cycle/cooling changes with performance and efficiency implications.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Body is a trim/appearance announcement with pricing and styling changes, not engineering or R&amp;D substance.</t>
+          <t>Mostly a trim-and-pricing announcement with styling details; no substantive engineering, validation, or platform content.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mostly a buyer’s guide and product overview; the body gives specs and comfort/feature notes, not meaningful engineering or R&amp;D detail.</t>
+          <t>Body is a consumer buyer’s guide with specs, trims, and feature rundown, not engineering/R&amp;D analysis or technical development insight.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Body is a consumer-facing discussion of headlight glare, survey results, and standards with little engineering detail beyond general safety context.</t>
+          <t>Body is mostly a consumer-facing glare survey and standards commentary, with little engineering depth beyond general headlight testing and maintenance.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>The body is a lifestyle/product note about manual crank windows and interior feel, with no substantive engineering or R&amp;D detail.</t>
+          <t>Body is mainly a consumer novelty about manual crank windows, with no substantive engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mostly a special-edition trim announcement with styling and pricing; no substantive engineering or R&amp;D content beyond basic engine specs.</t>
+          <t>Body is a special-edition announcement focused on badges, colors, and trim; no substantive engineering or R&amp;D detail beyond engine options.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mostly a first-look design and range overview with little engineering or validation substance beyond brief aero notes.</t>
+          <t>Mostly a first-look styling and range/trim article with little engineering or validation substance in the body.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mostly a vehicle feature preview with speculative specs and terrain modes; little substantive engineering or validation detail in the body.</t>
+          <t>Mostly a consumer first-look with specs and feature updates; the body offers little real engineering or validation detail beyond general hybrid and AWD mentions.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mostly a pricing and availability update for a production EV, with no substantive engineering, validation, or architecture discussion in the body.</t>
+          <t>Mostly a pricing/news blurb with range and charging specs; no substantive engineering, validation, or R&amp;D discussion.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mostly a concept reveal and product/future lineup story; the body gives only high-level platform and EREV mentions with little engineering detail.</t>
+          <t>The body is mostly a concept reveal and styling overview, with only brief mention of an EREV powertrain and body-on-frame platform.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Body has some suspension/hinge engineering details, but it is mainly a concept-feature wish list with limited R&amp;D substance.</t>
+          <t>Body has a couple of suspension/packaging details, but it is mostly a concept-feature wish list with little engineering depth or validation relevance.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Body is a crash-news anecdote with no engineering analysis, only damage description and author bio.</t>
+          <t>Body is a crash photo/news blurb with no engineering analysis beyond speculative damage description.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1969,22 +1969,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>not_selected</t>
+          <t>selected</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body has some drivetrain/off-road engineering discussion, but it is mostly opinion about desired features for a concept rather than substantive R&amp;D or validation detail.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Body has concrete drivetrain and off-road hardware discussion—manual transmission, lockers, ABS tuning, and true transfer case—relevant to vehicle engineering.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>final_markdown/motortrend/motortrend_final.md</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>skipped_not_selected</t>
+          <t>appended</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2096,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Body is just a site navigation/article listing page with categories and dates, not a substantive engineering article.</t>
+          <t>This is a MotorTrend homepage/category listing with navigation and article links, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2142,7 +2146,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mostly a buyer’s-guide overview with specs, trims, and features; little substantive engineering or validation detail in the body.</t>
+          <t>Mostly a buyer’s-guide overview with specs and features; little real engineering narrative beyond generic platform and charging mentions.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2174,7 +2178,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2183,7 +2187,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mostly a speculative model-year preview with broad feature and trim talk; the body lacks substantive engineering detail beyond general powertrain and tech guesses.</t>
+          <t>Mostly a speculative model-year preview with feature lists; it lacks substantive engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2224,7 +2228,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Contains some engineering details on powertrain, sensors, and MB.OS cooling, but it is mainly a consumer review/spec sheet with limited R&amp;D depth.</t>
+          <t>Contains some real engineering details on powertrain, sensors, cooling, and ADAS, but it is mostly a consumer product review with launch/spec focus rather than deep R&amp;D substance.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2256,7 +2260,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2265,7 +2269,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Body is mostly a consumer review and feature rundown; it has some powertrain and sensor details, but little substantive engineering analysis.</t>
+          <t>Mostly a luxury SUV review and feature recap; the body has some powertrain and sensor updates, but little substantive R&amp;D or validation detail.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2297,7 +2301,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2306,7 +2310,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Contains some EV architecture and Magma chassis/powertrain details, but it is mostly a consumer review with specs and feature listing rather than substantive R&amp;D or engineering analysis.</t>
+          <t>Mostly a consumer review/spec page; the body lacks deep engineering or validation detail beyond basic platform and charging specs.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2338,7 +2342,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mostly a consumer vehicle review with specs, trim, and feature lists; little substantive engineering or R&amp;D analysis in the body.</t>
+          <t>Mostly a consumer review with specs, trims, and feature lists; no substantive engineering or R&amp;D discussion beyond brief mentions of updates and driver-assist features.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>

--- a/extracted_urls/motortrend/motortrend_urls.xlsx
+++ b/extracted_urls/motortrend/motortrend_urls.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>This is a minivan ranking/list page with promotional testing claims, not a substantive engineering article.</t>
+          <t>This is a minivan ranking/listing page with no substantive engineering narrative or technical analysis in the body.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This is a ranking/list page with brief teaser links, not substantive engineering analysis or technical article content.</t>
+          <t>The body is a ranking/listing page with brief review blurbs, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>This is a ranking/listing page with teaser links, not a substantive engineering article, and the body lacks technical R&amp;D detail.</t>
+          <t>This is a ranking/listing page with brief teaser links, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>This is a ranking/list page with only brief teaser links and no substantive engineering or R&amp;D analysis in the body.</t>
+          <t>This is a ranking/listing page with teaser links and no substantive engineering narrative or technical analysis in the body.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Body gives concrete engineering details on charging architecture, port redesign, power conversion, and battery/software tradeoffs for EV development.</t>
+          <t>The body gives concrete engineering detail on charging architecture, port redesign, voltage conversion, battery chemistry, and validation decisions.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Body is mainly a consumer app review about EV road-trip charging convenience, with little engineering or R&amp;D substance.</t>
+          <t>Body is mainly a consumer app review about locating charging stations, with little engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Technical, but it’s mainly a home charging product review with limited engineering depth and no substantial automotive R&amp;D or vehicle system development content.</t>
+          <t>Body is a consumer home-charger product review with installation cost savings, not automotive R&amp;D or engineering work.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mostly a consumer review of a refreshed SUV, with only brief mention of the new transmission and driver-assist tech and little engineering depth.</t>
+          <t>Mostly a consumer vehicle overview with specs and feature talk; it lacks substantive engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mostly a facelift and pricing update with no substantive engineering or R&amp;D detail in the body.</t>
+          <t>Mostly a facelift/pricing update with trim and package changes; the body has little engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mostly a long-term ownership/review piece with performance impressions and option talk, not substantive engineering or R&amp;D analysis in the body.</t>
+          <t>Mostly a long-term ownership review of daily usability and trim/options, with only brief performance specs and no substantive engineering or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>This is a styling-and-features first look with no substantive engineering, validation, or architecture detail in the body.</t>
+          <t>Mostly a styling and feature-first vehicle preview with no real engineering, validation, or systems depth in the body.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>This is a retirement/profile piece with career highlights, not a substantive engineering article with technical development, validation, or architecture detail.</t>
+          <t>Mostly a retirement/profile piece with career highlights; the body lacks substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mostly a patriotic trim/package announcement with colors, badges, and interior cosmetics; no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a cosmetic package announcement with trim, graphics, and color details, not engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Body is just a cosmetic anniversary trim and paint announcement, with no engineering, validation, or systems detail.</t>
+          <t>Body is a cosmetic anniversary-package announcement with paint and trim details, not engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mostly a profile/interview about CMF design career and a personal lowrider build, with little engineering or R&amp;D substance beyond general color/materials work.</t>
+          <t>Body is mainly a profile of a CMF designer and her classic car, with only brief, high-level mentions of color/material strategy and no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Body is mostly a feature refresh and infotainment preview; the MB.OS and sensor stack mention is useful, but there’s little engineering depth or validation detail.</t>
+          <t>The body mainly describes a luxury SUV refresh and infotainment features; it mentions MB.OS and sensors, but gives little deep engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mostly a first-look product announcement with styling and feature comparisons; the body has little engineering depth beyond basic EV/driver-assist mentions.</t>
+          <t>Mostly a launch/feature overview with specs and styling, not substantive engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mostly a consumer road test with performance numbers and comfort impressions, not substantive engineering or R&amp;D analysis.</t>
+          <t>This is a consumer road test focused on value and driving feel, with only routine performance metrics and no meaningful engineering or R&amp;D depth.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Body is just a brief show roundup/listing with no engineering detail or substantive article narrative.</t>
+          <t>Body is just a brief show roundup with no engineering detail, mostly announcing debuts and concepts.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Contains some engineering-relevant software and interface changes, but the body is mostly a vehicle refresh with consumer tech and styling, not substantive R&amp;D detail.</t>
+          <t>The body is mostly a luxury SUV feature refresh; the real engineering content is limited to MB.OS, OTA, display monitoring, and cooling mentions without deeper validation or architecture detail.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mostly a product launch and specs recap; the body adds little engineering depth beyond basic powertrain, clearance, and mpg figures.</t>
+          <t>Mostly a product launch with specs and trim details; little substantive engineering or validation insight beyond general hybrid and suspension changes.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Body includes meaningful engineering detail on MQB evolution, electrical architecture, and Gen 5 turbo/Miller-cycle/cooling changes with performance and efficiency implications.</t>
+          <t>The body has real engineering detail on the MQB evolution, electrical architecture, and Gen 5 EA888 turbo/cooling/Miller-cycle changes that affect performance and efficiency.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mostly a trim-and-pricing announcement with styling details; no substantive engineering, validation, or platform content.</t>
+          <t>Mostly a trim/package announcement with color and cosmetic details; no substantive engineering or R&amp;D content in the body.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Body is a consumer buyer’s guide with specs, trims, and feature rundown, not engineering/R&amp;D analysis or technical development insight.</t>
+          <t>Mostly a buyer’s guide and feature review with specs and comfort notes, not substantive engineering or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Body is mostly a consumer-facing glare survey and standards commentary, with little engineering depth beyond general headlight testing and maintenance.</t>
+          <t>Discusses headlight glare policy and safety, but the body is mostly consumer-facing survey/news commentary with little engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Body is mainly a consumer novelty about manual crank windows, with no substantive engineering, validation, or architecture detail.</t>
+          <t>Body is a lifestyle/design note about manual crank windows, with no substantive engineering, validation, or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Body is a special-edition announcement focused on badges, colors, and trim; no substantive engineering or R&amp;D detail beyond engine options.</t>
+          <t>Mostly a special-edition trim announcement with styling and pricing; the body offers no substantive engineering or R&amp;D detail beyond engine options.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mostly a first-look styling and range/trim article with little engineering or validation substance in the body.</t>
+          <t>Mostly a first-look styling/range overview with marketing-level details; the body has little engineering or validation substance.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mostly a consumer first-look with specs and feature updates; the body offers little real engineering or validation detail beyond general hybrid and AWD mentions.</t>
+          <t>Mostly a model-change preview with specs and feature updates; the body lacks substantive engineering or validation detail beyond a few drivetrain and AWD mode mentions.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mostly a pricing/news blurb with range and charging specs; no substantive engineering, validation, or R&amp;D discussion.</t>
+          <t>Mostly a pricing/news item with range specs and charging notes, not substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The body is mostly a concept reveal and styling overview, with only brief mention of an EREV powertrain and body-on-frame platform.</t>
+          <t>Mostly a concept reveal with styling and market positioning; the body gives only a brief, high-level mention of body-on-frame and EREV with no real engineering detail.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Body has a couple of suspension/packaging details, but it is mostly a concept-feature wish list with little engineering depth or validation relevance.</t>
+          <t>Contains some chassis and suspension details, but it is mainly a concept-feature wishlist with little engineering depth or validation value.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Body is a crash photo/news blurb with no engineering analysis beyond speculative damage description.</t>
+          <t>Body is a crash-photo anecdote with no engineering analysis, validation insight, or technical discussion beyond superficial damage description.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body has concrete drivetrain and off-road hardware discussion—manual transmission, lockers, ABS tuning, and true transfer case—relevant to vehicle engineering.</t>
+          <t>The body contains concrete off-road engineering requirements like body-on-frame layout, lockers, transfer case, tires, and transmission choices.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>This is a MotorTrend homepage/category listing with navigation and article links, not a substantive engineering article.</t>
+          <t>This is mostly a homepage/category listing with navigation labels and article links, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mostly a buyer’s-guide overview with specs and features; little real engineering narrative beyond generic platform and charging mentions.</t>
+          <t>Mostly a buyer’s-guide overview with specs, trims, pricing, and features; little substantive engineering or R&amp;D analysis in the body.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mostly a speculative model-year preview with feature lists; it lacks substantive engineering, validation, or architecture detail.</t>
+          <t>Mostly a preview of a redesign with speculative trims and features; little substantive engineering detail beyond broad powertrain and infotainment guesses.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Contains some real engineering details on powertrain, sensors, cooling, and ADAS, but it is mostly a consumer product review with launch/spec focus rather than deep R&amp;D substance.</t>
+          <t>Mostly a consumer model refresh with specs and features; only light engineering detail on powertrain and sensor updates.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mostly a luxury SUV review and feature recap; the body has some powertrain and sensor updates, but little substantive R&amp;D or validation detail.</t>
+          <t>Body has some engineering detail on revised powertrains, sensors, and MB.OS, but it is mainly a luxury SUV review with launch/spec content rather than deep R&amp;D relevance.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mostly a consumer review/spec page; the body lacks deep engineering or validation detail beyond basic platform and charging specs.</t>
+          <t>Mostly a consumer review/spec page; it mentions platform, charging, and Magma tuning but gives little substantive engineering or validation depth.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mostly a consumer review with specs, trims, and feature lists; no substantive engineering or R&amp;D discussion beyond brief mentions of updates and driver-assist features.</t>
+          <t>Mostly a consumer vehicle review with specs and features; little substantive engineering or R&amp;D analysis beyond brief mentions of suspension and driver-assist tuning.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
